--- a/lab-standards/Mahila-Polytechnic-lab-standard.xlsx
+++ b/lab-standards/Mahila-Polytechnic-lab-standard.xlsx
@@ -558,6 +558,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -570,6 +574,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -639,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -661,7 +671,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -683,7 +695,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
       </c>
@@ -705,7 +719,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -727,7 +743,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -749,7 +767,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -771,7 +791,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -793,7 +815,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -815,7 +839,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>9</v>
       </c>
@@ -837,7 +863,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -859,7 +887,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -881,7 +911,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -901,7 +933,9 @@
         </is>
       </c>
       <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -927,7 +961,9 @@
       <c r="C29" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -949,7 +985,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -969,7 +1007,9 @@
         </is>
       </c>
       <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -995,7 +1035,9 @@
       <c r="C32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>9</v>
       </c>
@@ -1015,7 +1057,9 @@
         </is>
       </c>
       <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>9</v>
       </c>
@@ -1039,7 +1083,9 @@
         </is>
       </c>
       <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -1065,7 +1111,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>10</v>
       </c>
@@ -1087,7 +1135,9 @@
       <c r="C36" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>8</v>
       </c>
@@ -1109,7 +1159,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>8</v>
       </c>
@@ -1131,7 +1183,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>9</v>
       </c>
@@ -1153,7 +1207,9 @@
       <c r="C39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>9</v>
       </c>
@@ -1175,7 +1231,9 @@
       <c r="C40" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>7</v>
       </c>
@@ -1195,7 +1253,9 @@
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>6</v>
       </c>
@@ -1219,7 +1279,9 @@
         </is>
       </c>
       <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>6</v>
       </c>
@@ -1243,7 +1305,9 @@
         </is>
       </c>
       <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
@@ -1393,6 +1457,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1405,6 +1473,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1474,7 +1546,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1496,7 +1570,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1518,7 +1594,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1540,7 +1618,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -1562,7 +1642,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -1584,7 +1666,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -1606,7 +1690,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -1628,7 +1714,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -1650,7 +1738,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>9</v>
       </c>
@@ -1672,7 +1762,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -1694,7 +1786,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -1716,7 +1810,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -1738,7 +1834,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -1760,7 +1858,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -1782,7 +1882,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1804,7 +1906,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -1826,7 +1930,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -1852,7 +1958,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1874,7 +1982,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1896,7 +2006,9 @@
       <c r="C35" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1918,7 +2030,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -1940,7 +2054,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -1962,7 +2078,9 @@
       <c r="C38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -1984,7 +2102,9 @@
       <c r="C39" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -2006,7 +2126,9 @@
       <c r="C40" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>5</v>
       </c>
@@ -2026,7 +2148,9 @@
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -2102,8 +2226,8 @@
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="C8:G8"/>
   </mergeCells>
@@ -2176,6 +2300,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2189,6 +2317,10 @@
 Workshop		: 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2258,7 +2390,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -2280,7 +2414,9 @@
       <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -2302,7 +2438,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -2324,7 +2462,9 @@
       <c r="C19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -2346,7 +2486,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2368,7 +2510,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2390,7 +2534,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -2412,7 +2558,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2434,7 +2582,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2456,7 +2606,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2478,7 +2630,9 @@
       <c r="C26" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -2500,7 +2654,9 @@
       <c r="C27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -2522,7 +2678,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -2544,7 +2702,9 @@
       <c r="C29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2566,7 +2726,9 @@
       <c r="C30" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -2588,7 +2750,9 @@
       <c r="C31" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -2610,7 +2774,9 @@
       <c r="C32" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -2632,7 +2798,9 @@
       <c r="C33" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -2654,7 +2822,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -2676,7 +2846,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>8</v>
       </c>
@@ -2698,7 +2870,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>8</v>
       </c>
@@ -2720,7 +2894,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -2742,7 +2918,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
